--- a/data/content/allocation_norms/ncf_chapterwise_period_allocation.xlsx
+++ b/data/content/allocation_norms/ncf_chapterwise_period_allocation.xlsx
@@ -9868,7 +9868,7 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>

--- a/data/content/allocation_norms/ncf_chapterwise_period_allocation.xlsx
+++ b/data/content/allocation_norms/ncf_chapterwise_period_allocation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kumar_radhakrishnan/main/kumar/AI/aruvi-saas/data/content/allocation_norms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B88E0F-D85A-A644-8C3E-3EEA9F8BE7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{547743E3-2A27-EF47-B335-33869F72B167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13580" yWindow="980" windowWidth="16380" windowHeight="13560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="693">
   <si>
     <t>Chapter-wise Period Allocation</t>
   </si>
@@ -2107,6 +2107,54 @@
   </si>
   <si>
     <t>X</t>
+  </si>
+  <si>
+    <t>Duration assumption</t>
+  </si>
+  <si>
+    <r>
+      <t>40 min</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — classes III–VII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>45 min</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — class VIII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>50 min</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — class IX</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2116,7 +2164,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.####"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2207,8 +2255,15 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2225,6 +2280,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEEE7D8"/>
         <bgColor rgb="FFFBE5C8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2301,13 +2362,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2358,6 +2414,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2622,7 +2686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -2630,408 +2694,421 @@
     <col min="3" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-    </row>
-    <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+    </row>
+    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+    </row>
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>689</v>
+      </c>
+      <c r="H4" s="26"/>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="2">
         <f>IF(COUNTIFS(budget!$A:$A,$B$4,budget!$B:$B,$B$5)=0,"",IF(SUMIFS(budget!$C:$C,budget!$A:$A,$B$4,budget!$B:$B,$B$5)=0,"",SUMIFS(budget!$C:$C,budget!$A:$A,$B$4,budget!$B:$B,$B$5)))</f>
-        <v>245</v>
-      </c>
-      <c r="C6" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="str">
+      <c r="G6" s="24" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="23" t="str">
         <f>IF($B$4="","Choose a subject and class, then enter your annual budget.",IF(COUNTIFS(Chapters!$A:$A,$B$4,Chapters!$B:$B,$B$5)=0,"No chapters found for this subject and class - try another combination.",IF($B$6="","Enter your annual budget (periods) above.","")))</f>
         <v/>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="G7" s="24" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="9">
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
         <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
         <v>1</v>
       </c>
-      <c r="B10" s="10" t="str">
+      <c r="B10" s="7" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Chapter 1: Understanding Social Science</v>
-      </c>
-      <c r="C10" s="11">
+        <v>Fun with Friends (Fun with Friends)</v>
+      </c>
+      <c r="C10" s="8">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>13</v>
-      </c>
-      <c r="D10" s="12">
+        <v>5.5</v>
+      </c>
+      <c r="D10" s="9">
         <f>IF(OR($C10="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C10)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C10)-$C10)/$C$28*$B$6,0))</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
         <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
         <v>2</v>
       </c>
-      <c r="B11" s="10" t="str">
+      <c r="B11" s="7" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Chapter 2: Shaping of the Earth's Surface</v>
-      </c>
-      <c r="C11" s="11">
+        <v>Colours (Fun with Friends)</v>
+      </c>
+      <c r="C11" s="8">
+        <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
+        <v>6.5</v>
+      </c>
+      <c r="D11" s="9">
+        <f>IF(OR($C11="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C11)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C11)-$C11)/$C$28*$B$6,0))</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
+        <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="B12" s="7" t="str">
+        <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
+        <v>Badal and Moti (Badal and Moti)</v>
+      </c>
+      <c r="C12" s="8">
+        <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
+        <v>11.5</v>
+      </c>
+      <c r="D12" s="9">
+        <f>IF(OR($C12="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C12)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C12)-$C12)/$C$28*$B$6,0))</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
+        <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
+        <v>4</v>
+      </c>
+      <c r="B13" s="7" t="str">
+        <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
+        <v>Best Friends (Best Friends)</v>
+      </c>
+      <c r="C13" s="8">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
         <v>10</v>
       </c>
-      <c r="D11" s="12">
-        <f>IF(OR($C11="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C11)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C11)-$C11)/$C$28*$B$6,0))</f>
+      <c r="D13" s="9">
+        <f>IF(OR($C13="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C13)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C13)-$C13)/$C$28*$B$6,0))</f>
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="9">
-        <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>3</v>
-      </c>
-      <c r="B12" s="10" t="str">
-        <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Chapter 3: Atmosphere and Climate</v>
-      </c>
-      <c r="C12" s="11">
-        <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>11</v>
-      </c>
-      <c r="D12" s="12">
-        <f>IF(OR($C12="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C12)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C12)-$C12)/$C$28*$B$6,0))</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="9">
-        <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>4</v>
-      </c>
-      <c r="B13" s="10" t="str">
-        <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Chapter 4: Early Humans and Beginning of Civilisation</v>
-      </c>
-      <c r="C13" s="11">
-        <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>17</v>
-      </c>
-      <c r="D13" s="12">
-        <f>IF(OR($C13="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C13)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C13)-$C13)/$C$28*$B$6,0))</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="9">
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="6">
         <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
         <v>5</v>
       </c>
-      <c r="B14" s="10" t="str">
+      <c r="B14" s="7" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Chapter 5: State and Society up to 1000 CE</v>
-      </c>
-      <c r="C14" s="11">
+        <v>What do You do? (Best Friends)</v>
+      </c>
+      <c r="C14" s="8">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>19</v>
-      </c>
-      <c r="D14" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="D14" s="9">
         <f>IF(OR($C14="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C14)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C14)-$C14)/$C$28*$B$6,0))</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="6">
         <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
         <v>6</v>
       </c>
-      <c r="B15" s="10" t="str">
+      <c r="B15" s="7" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Chapter 6: Democracy</v>
-      </c>
-      <c r="C15" s="11">
+        <v>Toys and Games (Picture Reading) (Toys and Games)</v>
+      </c>
+      <c r="C15" s="8">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>17</v>
-      </c>
-      <c r="D15" s="12">
+        <v>5.5</v>
+      </c>
+      <c r="D15" s="9">
         <f>IF(OR($C15="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C15)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C15)-$C15)/$C$28*$B$6,0))</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="6">
         <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
         <v>7</v>
       </c>
-      <c r="B16" s="10" t="str">
+      <c r="B16" s="7" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Chapter 7: Elections</v>
-      </c>
-      <c r="C16" s="11">
+        <v>Out in the Garden (Toys and Games)</v>
+      </c>
+      <c r="C16" s="8">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>8</v>
-      </c>
-      <c r="D16" s="12">
+        <v>6.5</v>
+      </c>
+      <c r="D16" s="9">
         <f>IF(OR($C16="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C16)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C16)-$C16)/$C$28*$B$6,0))</f>
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="9">
+      <c r="A17" s="6">
         <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
         <v>8</v>
       </c>
-      <c r="B17" s="10" t="str">
+      <c r="B17" s="7" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Chapter 8: Building Blocks in Economics: The Problem of Choice</v>
-      </c>
-      <c r="C17" s="11">
+        <v>Talking Toys (Talking Toys)</v>
+      </c>
+      <c r="C17" s="8">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>6</v>
-      </c>
-      <c r="D17" s="12">
+        <v>10</v>
+      </c>
+      <c r="D17" s="9">
         <f>IF(OR($C17="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C17)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C17)-$C17)/$C$28*$B$6,0))</f>
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="9">
+      <c r="A18" s="6">
         <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
         <v>9</v>
       </c>
-      <c r="B18" s="10" t="str">
+      <c r="B18" s="7" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Chapter 9: The Price Puzzle: What Drives the Market</v>
-      </c>
-      <c r="C18" s="11">
+        <v>Paper Boats (Paper Boats)</v>
+      </c>
+      <c r="C18" s="8">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>6</v>
-      </c>
-      <c r="D18" s="12">
+        <v>8.5</v>
+      </c>
+      <c r="D18" s="9">
         <f>IF(OR($C18="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C18)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C18)-$C18)/$C$28*$B$6,0))</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="9">
+      <c r="A19" s="6">
         <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
         <v>10</v>
       </c>
-      <c r="B19" s="10" t="str">
+      <c r="B19" s="7" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Chapter 10: (Placeholder — awaiting NCERT release)</v>
-      </c>
-      <c r="C19" s="11">
+        <v>Good Food — Picture Reading (The Big Laddoo)</v>
+      </c>
+      <c r="C19" s="8">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>12</v>
-      </c>
-      <c r="D19" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="D19" s="9">
         <f>IF(OR($C19="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C19)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C19)-$C19)/$C$28*$B$6,0))</f>
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="9">
+      <c r="A20" s="6">
         <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
         <v>11</v>
       </c>
-      <c r="B20" s="10" t="str">
+      <c r="B20" s="7" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Chapter 11: (Placeholder — awaiting NCERT release)</v>
-      </c>
-      <c r="C20" s="11">
+        <v>The Big Laddoo (The Big Laddoo)</v>
+      </c>
+      <c r="C20" s="8">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
+        <v>11.5</v>
+      </c>
+      <c r="D20" s="9">
+        <f>IF(OR($C20="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C20)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C20)-$C20)/$C$28*$B$6,0))</f>
         <v>12</v>
       </c>
-      <c r="D20" s="12">
-        <f>IF(OR($C20="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C20)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C20)-$C20)/$C$28*$B$6,0))</f>
-        <v>13</v>
-      </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="9">
+      <c r="A21" s="6">
         <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
         <v>12</v>
       </c>
-      <c r="B21" s="10" t="str">
+      <c r="B21" s="7" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Chapter 12: (Placeholder — awaiting NCERT release)</v>
-      </c>
-      <c r="C21" s="11">
+        <v>Thank God! (Thank God!)</v>
+      </c>
+      <c r="C21" s="8">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>12</v>
-      </c>
-      <c r="D21" s="12">
+        <v>8.5</v>
+      </c>
+      <c r="D21" s="9">
         <f>IF(OR($C21="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C21)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C21)-$C21)/$C$28*$B$6,0))</f>
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="9">
+      <c r="A22" s="6">
         <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
         <v>13</v>
       </c>
-      <c r="B22" s="10" t="str">
+      <c r="B22" s="7" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Chapter 13: (Placeholder — awaiting NCERT release)</v>
-      </c>
-      <c r="C22" s="11">
+        <v>Madhu's Wish (Madhu's Wish)</v>
+      </c>
+      <c r="C22" s="8">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>12</v>
-      </c>
-      <c r="D22" s="12">
+        <v>10</v>
+      </c>
+      <c r="D22" s="9">
         <f>IF(OR($C22="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C22)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C22)-$C22)/$C$28*$B$6,0))</f>
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="9">
+      <c r="A23" s="6">
         <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
         <v>14</v>
       </c>
-      <c r="B23" s="10" t="str">
+      <c r="B23" s="7" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Chapter 14: (Placeholder — awaiting NCERT release)</v>
-      </c>
-      <c r="C23" s="11">
+        <v>The Sky — Picture Reading (Night)</v>
+      </c>
+      <c r="C23" s="8">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>12</v>
-      </c>
-      <c r="D23" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="D23" s="9">
         <f>IF(OR($C23="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C23)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C23)-$C23)/$C$28*$B$6,0))</f>
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="9">
+      <c r="A24" s="6">
         <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
         <v>15</v>
       </c>
-      <c r="B24" s="10" t="str">
+      <c r="B24" s="7" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Chapter 15: (Placeholder — awaiting NCERT release)</v>
-      </c>
-      <c r="C24" s="11">
+        <v>Night (Night)</v>
+      </c>
+      <c r="C24" s="8">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>12</v>
-      </c>
-      <c r="D24" s="12">
+        <v>6.5</v>
+      </c>
+      <c r="D24" s="9">
         <f>IF(OR($C24="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C24)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C24)-$C24)/$C$28*$B$6,0))</f>
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="9">
+      <c r="A25" s="6">
         <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
         <v>16</v>
       </c>
-      <c r="B25" s="10" t="str">
+      <c r="B25" s="7" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Chapter 16: (Placeholder — awaiting NCERT release)</v>
-      </c>
-      <c r="C25" s="11">
+        <v>Chanda Mama Counts the Stars (Chanda Mama Counts the Stars)</v>
+      </c>
+      <c r="C25" s="8">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>12</v>
-      </c>
-      <c r="D25" s="12">
+        <v>8.5</v>
+      </c>
+      <c r="D25" s="9">
         <f>IF(OR($C25="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C25)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C25)-$C25)/$C$28*$B$6,0))</f>
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="9">
+      <c r="A26" s="6">
         <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
         <v>17</v>
       </c>
-      <c r="B26" s="10" t="str">
+      <c r="B26" s="7" t="str">
         <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Chapter 17: (Placeholder — awaiting NCERT release)</v>
-      </c>
-      <c r="C26" s="11">
+        <v>Chandrayaan (Chandrayaan)</v>
+      </c>
+      <c r="C26" s="8">
         <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
+        <v>10</v>
+      </c>
+      <c r="D26" s="9">
+        <f>IF(OR($C26="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C26)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C26)-$C26)/$C$28*$B$6,0))</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="str">
+        <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
+        <v/>
+      </c>
+      <c r="B27" s="7" t="str">
+        <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C27" s="8" t="str">
+        <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="9" t="str">
+        <f>IF(OR($C27="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C27)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C27)-$C27)/$C$28*$B$6,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="12">
-        <f>IF(OR($C26="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C26)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C26)-$C26)/$C$28*$B$6,0))</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="9">
-        <f>IFERROR(INDEX(Chapters!$C:$C,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>18</v>
-      </c>
-      <c r="B27" s="10" t="str">
-        <f>IFERROR(INDEX(Chapters!$D:$D,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>Chapter 18: (Placeholder — awaiting NCERT release)</v>
-      </c>
-      <c r="C27" s="11">
-        <f>IFERROR(INDEX(Chapters!$E:$E,MATCH($B$4&amp;"|"&amp;$B$5&amp;"|"&amp;(ROW()-9),Chapters!$F:$F,0)),"")</f>
-        <v>12</v>
-      </c>
-      <c r="D27" s="12">
-        <f>IF(OR($C27="",$C$28=0,$B$6=""),"",ROUND(SUM($C$10:$C27)/$C$28*$B$6,0)-ROUND((SUM($C$10:$C27)-$C27)/$C$28*$B$6,0))</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="14">
+      <c r="C28" s="11">
         <f>SUM(C10:C27)</f>
-        <v>215</v>
-      </c>
-      <c r="D28" s="15">
+        <v>129.5</v>
+      </c>
+      <c r="D28" s="12">
         <f>SUM(D10:D27)</f>
-        <v>245</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -3074,25 +3151,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -10905,436 +10982,436 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="16"/>
+    <col min="2" max="2" width="10.83203125" style="13"/>
     <col min="3" max="3" width="12.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="20" t="s">
+      <c r="A2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="18">
         <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="18">
         <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="16" t="s">
         <v>417</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="18">
         <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="16" t="s">
         <v>687</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="C5" s="21"/>
+      <c r="C5" s="18"/>
     </row>
     <row r="6" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="16" t="s">
         <v>518</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="18">
         <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="20" t="s">
+      <c r="A7" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="18">
         <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="18">
         <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="16" t="s">
         <v>417</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="18">
         <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="16" t="s">
         <v>687</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="21"/>
+      <c r="C10" s="18"/>
     </row>
     <row r="11" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="16" t="s">
         <v>518</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="18">
         <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="20" t="s">
+      <c r="A12" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="18">
         <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="18">
         <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="16" t="s">
         <v>417</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="21"/>
+      <c r="C14" s="18"/>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="16" t="s">
         <v>687</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="18">
         <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="16" t="s">
         <v>518</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="21"/>
+      <c r="C16" s="18"/>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="22" t="s">
+      <c r="A17" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="19" t="s">
         <v>688</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="18">
         <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="19" t="s">
         <v>688</v>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="18">
         <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="16" t="s">
         <v>417</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="19" t="s">
         <v>688</v>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="18">
         <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="16" t="s">
         <v>687</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="19" t="s">
         <v>688</v>
       </c>
-      <c r="C20" s="21"/>
+      <c r="C20" s="18"/>
     </row>
     <row r="21" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="16" t="s">
         <v>518</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="19" t="s">
         <v>688</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="18">
         <v>245</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="22" t="s">
+      <c r="A22" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="18">
         <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="18">
         <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="16" t="s">
         <v>417</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="18">
         <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="16" t="s">
         <v>687</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="21"/>
+      <c r="C25" s="18"/>
     </row>
     <row r="26" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="16" t="s">
         <v>518</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="C26" s="21">
+      <c r="C26" s="18">
         <v>210</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" s="22" t="s">
+      <c r="A27" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="21">
+      <c r="C27" s="18">
         <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="21">
+      <c r="C28" s="18">
         <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="16" t="s">
         <v>417</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="21"/>
+      <c r="C29" s="18"/>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="16" t="s">
         <v>687</v>
       </c>
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C30" s="18">
         <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="16" t="s">
         <v>518</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="21"/>
+      <c r="C31" s="18"/>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" s="22" t="s">
+      <c r="A32" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="21">
+      <c r="C32" s="18">
         <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="19" t="s">
+      <c r="A33" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="21">
+      <c r="C33" s="18">
         <v>160</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="19" t="s">
+      <c r="A34" s="16" t="s">
         <v>417</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C34" s="21"/>
+      <c r="C34" s="18"/>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="16" t="s">
         <v>687</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="21">
+      <c r="C35" s="18">
         <v>140</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="19" t="s">
+      <c r="A36" s="16" t="s">
         <v>518</v>
       </c>
-      <c r="B36" s="22" t="s">
+      <c r="B36" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="21"/>
+      <c r="C36" s="18"/>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="B37" s="20" t="s">
+      <c r="A37" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="C37" s="21">
+      <c r="C37" s="18">
         <v>140</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="19" t="s">
+      <c r="A38" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="C38" s="21">
+      <c r="C38" s="18">
         <v>180</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="23" t="s">
+      <c r="A39" s="20" t="s">
         <v>417</v>
       </c>
-      <c r="B39" s="20" t="s">
+      <c r="B39" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="C39" s="21">
+      <c r="C39" s="18">
         <v>180</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="23" t="s">
+      <c r="A40" s="20" t="s">
         <v>687</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="C40" s="21"/>
+      <c r="C40" s="18"/>
     </row>
     <row r="41" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="23" t="s">
+      <c r="A41" s="20" t="s">
         <v>518</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="C41" s="21">
+      <c r="C41" s="18">
         <v>210</v>
       </c>
     </row>
